--- a/Clustering/Lube Oil System/DBSCAN/clustering_lube_oil_g11/kpis.xlsx
+++ b/Clustering/Lube Oil System/DBSCAN/clustering_lube_oil_g11/kpis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RNN_projects\Clustering\Lube Oil System\DBSCAN\clustering_lube_oil_g11\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E30E61E-296D-46DF-AF17-965A61E18CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C80653-F9D3-42EC-86B9-EB99AA71186A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="5" activeTab="7" xr2:uid="{5363877E-F927-496C-B699-B2B87BF23985}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="6" xr2:uid="{5363877E-F927-496C-B699-B2B87BF23985}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId1"/>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="377">
   <si>
     <t>نام شاخص</t>
   </si>
@@ -3262,9 +3262,6 @@
     <t>سرانه تولید پسماند (گرم بر نفر در روز)</t>
   </si>
   <si>
-    <t>سرانه مصرف آب بهداشتی (لیتر بر نفر در روز)</t>
-  </si>
-  <si>
     <t>نسبت روز‌های خارج از مدار آنالایزر دود به حد مجاز اعلامی محیط زیست</t>
   </si>
   <si>
@@ -3452,6 +3449,48 @@
   </si>
   <si>
     <t>بهینه سازی راندمان و مصرف سوخت</t>
+  </si>
+  <si>
+    <t>آمادگی محقق شده به آمادگی پیش بینی شده (درصد)</t>
+  </si>
+  <si>
+    <t>درصد اجرای PM‌هایبخش شیمی</t>
+  </si>
+  <si>
+    <t>درصد دستورکار‌های منتظر قطعه (درصد)</t>
+  </si>
+  <si>
+    <t>میانگین زمان تعمیر (ساعت)- MTTR</t>
+  </si>
+  <si>
+    <t>میانگین زمان  بین خرابی‌ها (ساعت)- MTBF</t>
+  </si>
+  <si>
+    <t>درصد تحقق فعالیت‌های دوره‌ای</t>
+  </si>
+  <si>
+    <t>درصد دستورکار‌های اصلاحی باز</t>
+  </si>
+  <si>
+    <t>قابلیت دسترسی فنی واحدOH/EH</t>
+  </si>
+  <si>
+    <t>درصد ابزار‌های اندازه‌گیری  کالیبره شده</t>
+  </si>
+  <si>
+    <t>متوسط زمان تأمین خدمات فنی (روز)</t>
+  </si>
+  <si>
+    <t>متوسط زمان انعقاد قرارداد خدمات فنی (روز)</t>
+  </si>
+  <si>
+    <t>متوسط زمان انعقاد قرارداد تأمین کالا (روز)</t>
+  </si>
+  <si>
+    <t>درصد PM‌های انجام شده (درصد)</t>
+  </si>
+  <si>
+    <t>این متن رو کپی کن و در اکسل پیست کن (با جداکننده Tab یا مستقیم در سلول A1 پیست کن، اکسل خودش ستون‌ها رو جدا می‌کنه).</t>
   </si>
 </sst>
 </file>
@@ -3575,7 +3614,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -3641,11 +3680,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3725,12 +3777,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
@@ -3753,10 +3799,19 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment readingOrder="2"/>
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+      <alignment wrapText="1" readingOrder="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4080,20 +4135,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="37" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
     </row>
     <row r="3" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
     </row>
     <row r="4" spans="1:3" ht="37.5" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
@@ -5695,7 +5750,7 @@
     </row>
     <row r="2" spans="1:4" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B2" s="24">
         <v>22</v>
@@ -5899,23 +5954,23 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10CB85A6-F59B-4081-BD62-0A7B6AED97E2}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="13.25" style="22" customWidth="1"/>
-    <col min="3" max="3" width="37.375" style="32" customWidth="1"/>
+    <col min="3" max="3" width="37.375" style="30" customWidth="1"/>
     <col min="4" max="4" width="53.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.5">
       <c r="A1" s="16" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>290</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="29" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="25" t="s">
@@ -5924,7 +5979,7 @@
     </row>
     <row r="2" spans="1:4" ht="37.5" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B2" s="24">
         <v>29</v>
@@ -6040,58 +6095,36 @@
       </c>
     </row>
     <row r="12" spans="1:4" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="B12" s="36">
+      <c r="B12" s="34">
         <v>129</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="D12" s="37" t="s">
+      <c r="D12" s="35" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="B13" s="36">
+      <c r="B13" s="34">
         <v>130</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="D13" s="37" t="s">
+      <c r="D13" s="35" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="B14" s="36">
+      <c r="B14" s="34">
         <v>131</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="D14" s="37" t="s">
+      <c r="D14" s="35" t="s">
         <v>160</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="B15" s="33">
-        <v>132</v>
-      </c>
-      <c r="C15" s="34" t="s">
-        <v>300</v>
-      </c>
-      <c r="D15" s="35" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="37.5" x14ac:dyDescent="0.2">
-      <c r="B16" s="33">
-        <v>133</v>
-      </c>
-      <c r="C16" s="34" t="s">
-        <v>301</v>
-      </c>
-      <c r="D16" s="35" t="s">
-        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -6102,25 +6135,25 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70719E36-25FB-4C76-943D-901E31BC6E17}">
   <sheetPr>
-    <tabColor rgb="FFFF0000"/>
+    <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D104"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="45.75" customWidth="1"/>
     <col min="2" max="2" width="16.875" style="22" customWidth="1"/>
-    <col min="3" max="3" width="37.875" style="38" customWidth="1"/>
+    <col min="3" max="3" width="37.875" style="40" customWidth="1"/>
     <col min="4" max="4" width="41.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.5">
       <c r="A1" s="16" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>290</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="29" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="25" t="s">
@@ -6129,177 +6162,733 @@
     </row>
     <row r="2" spans="1:4" ht="37.5" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
-        <v>359</v>
-      </c>
-      <c r="B2" s="24">
-        <v>29</v>
+        <v>358</v>
+      </c>
+      <c r="B2" s="9">
+        <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>199</v>
+        <v>26</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="37.5" x14ac:dyDescent="0.2">
       <c r="A3" s="12"/>
-      <c r="B3" s="24">
-        <v>30</v>
+      <c r="B3" s="9">
+        <v>23</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>200</v>
+        <v>27</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="37.5" x14ac:dyDescent="0.2">
       <c r="A4" s="12"/>
-      <c r="B4" s="24">
-        <v>32</v>
+      <c r="B4" s="9">
+        <v>24</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>202</v>
+        <v>283</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="37.5" x14ac:dyDescent="0.2">
       <c r="A5" s="12"/>
-      <c r="B5" s="24">
+      <c r="B5" s="9">
+        <v>25</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="37.5" x14ac:dyDescent="0.2">
+      <c r="B6" s="9">
+        <v>26</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="37.5" x14ac:dyDescent="0.2">
+      <c r="B7" s="9">
+        <v>27</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="37.5" x14ac:dyDescent="0.2">
+      <c r="B8" s="9">
+        <v>28</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="37.5" x14ac:dyDescent="0.2">
+      <c r="B9" s="9">
+        <v>29</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="37.5" x14ac:dyDescent="0.2">
-      <c r="B6" s="24">
+      <c r="D9" s="20" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="37.5" x14ac:dyDescent="0.2">
+      <c r="B10" s="9">
+        <v>30</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="37.5" x14ac:dyDescent="0.2">
-      <c r="B7" s="24">
+      <c r="D10" s="20" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="75" x14ac:dyDescent="0.2">
+      <c r="B11" s="9">
+        <v>31</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="37.5" x14ac:dyDescent="0.2">
-      <c r="B8" s="24">
-        <v>36</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="37.5" x14ac:dyDescent="0.2">
-      <c r="B9" s="24">
+      <c r="D11" s="21" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="37.5" x14ac:dyDescent="0.2">
+      <c r="B12" s="9">
         <v>37</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D9" s="3" t="s">
+      <c r="C12" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="D12" s="20" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="37.5" x14ac:dyDescent="0.2">
-      <c r="B10" s="24">
-        <v>38</v>
-      </c>
-      <c r="C10" s="3" t="s">
+    <row r="13" spans="1:4" ht="37.5" x14ac:dyDescent="0.2">
+      <c r="B13" s="9">
         <v>41</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="37.5" x14ac:dyDescent="0.2">
-      <c r="B11" s="24">
-        <v>39</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="37.5" x14ac:dyDescent="0.2">
-      <c r="B12" s="24">
+      <c r="C13" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="37.5" x14ac:dyDescent="0.2">
+      <c r="B14" s="9">
+        <v>42</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="37.5" x14ac:dyDescent="0.2">
+      <c r="B15" s="9">
+        <v>44</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="168.75" x14ac:dyDescent="0.2">
+      <c r="B16" s="9">
+        <v>45</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" ht="168.75" x14ac:dyDescent="0.2">
+      <c r="B17" s="9">
+        <v>46</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" ht="37.5" x14ac:dyDescent="0.2">
+      <c r="B18" s="9">
+        <v>47</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" ht="37.5" x14ac:dyDescent="0.2">
+      <c r="B19" s="9">
+        <v>48</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" ht="37.5" x14ac:dyDescent="0.2">
+      <c r="B20" s="9">
+        <v>49</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" ht="37.5" x14ac:dyDescent="0.2">
+      <c r="B21" s="9">
+        <v>50</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" ht="37.5" x14ac:dyDescent="0.2">
+      <c r="B22" s="9">
+        <v>51</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" ht="37.5" x14ac:dyDescent="0.2">
+      <c r="B23" s="9">
+        <v>52</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" ht="37.5" x14ac:dyDescent="0.2">
+      <c r="B24" s="9">
+        <v>53</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" ht="37.5" x14ac:dyDescent="0.2">
+      <c r="B25" s="9">
+        <v>54</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" ht="37.5" x14ac:dyDescent="0.2">
+      <c r="B26" s="9">
+        <v>55</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" ht="56.25" x14ac:dyDescent="0.2">
+      <c r="B27" s="9">
+        <v>56</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" ht="75" x14ac:dyDescent="0.2">
+      <c r="B28" s="9">
+        <v>57</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" ht="37.5" x14ac:dyDescent="0.2">
+      <c r="B29" s="9">
+        <v>58</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="B30" s="9">
+        <v>61</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" ht="37.5" x14ac:dyDescent="0.2">
+      <c r="B31" s="9">
+        <v>66</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D31" s="20" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" ht="56.25" x14ac:dyDescent="0.2">
+      <c r="B32" s="9">
+        <v>67</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D32" s="21" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" ht="37.5" x14ac:dyDescent="0.2">
+      <c r="B33" s="9">
+        <v>111</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="37.5" x14ac:dyDescent="0.2">
-      <c r="B13" s="24">
-        <v>130</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="B14" s="24">
-        <v>131</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="B15" s="24">
-        <v>132</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="37.5" x14ac:dyDescent="0.2">
-      <c r="B16" s="24">
-        <v>133</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>164</v>
+      <c r="D33" s="21" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" ht="38.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="9">
+        <v>142</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="D34" s="39" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B57" s="22" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B61" s="22" t="s">
+        <v>290</v>
+      </c>
+      <c r="C61" s="40" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B62" s="22">
+        <v>22</v>
+      </c>
+      <c r="C62" s="40" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B63" s="22">
+        <v>23</v>
+      </c>
+      <c r="C63" s="40" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B64" s="22">
+        <v>24</v>
+      </c>
+      <c r="C64" s="40" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B65" s="22">
+        <v>25</v>
+      </c>
+      <c r="C65" s="40" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B66" s="22">
+        <v>26</v>
+      </c>
+      <c r="C66" s="40" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B67" s="22">
+        <v>27</v>
+      </c>
+      <c r="C67" s="40" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B68" s="22">
+        <v>28</v>
+      </c>
+      <c r="C68" s="40" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B69" s="22">
+        <v>29</v>
+      </c>
+      <c r="C69" s="40" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B70" s="22">
+        <v>30</v>
+      </c>
+      <c r="C70" s="40" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="71" spans="2:3" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B71" s="22">
+        <v>31</v>
+      </c>
+      <c r="C71" s="40" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="72" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B72" s="22">
+        <v>37</v>
+      </c>
+      <c r="C72" s="40" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B73" s="22">
+        <v>41</v>
+      </c>
+      <c r="C73" s="40" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B74" s="22">
+        <v>42</v>
+      </c>
+      <c r="C74" s="40" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B75" s="22">
+        <v>43</v>
+      </c>
+      <c r="C75" s="40" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B76" s="22">
+        <v>44</v>
+      </c>
+      <c r="C76" s="40" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B77" s="22">
+        <v>45</v>
+      </c>
+      <c r="C77" s="40" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B78" s="22">
+        <v>46</v>
+      </c>
+      <c r="C78" s="40" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B79" s="22">
+        <v>47</v>
+      </c>
+      <c r="C79" s="40" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B80" s="22">
+        <v>48</v>
+      </c>
+      <c r="C80" s="40" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B81" s="22">
+        <v>49</v>
+      </c>
+      <c r="C81" s="40" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B82" s="22">
+        <v>50</v>
+      </c>
+      <c r="C82" s="40" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="83" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B83" s="22">
+        <v>51</v>
+      </c>
+      <c r="C83" s="40" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B84" s="22">
+        <v>52</v>
+      </c>
+      <c r="C84" s="40" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="85" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B85" s="22">
+        <v>53</v>
+      </c>
+      <c r="C85" s="40" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="86" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B86" s="22">
+        <v>54</v>
+      </c>
+      <c r="C86" s="40" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="87" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B87" s="22">
+        <v>55</v>
+      </c>
+      <c r="C87" s="40" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="88" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B88" s="22">
+        <v>56</v>
+      </c>
+      <c r="C88" s="40" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="89" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B89" s="22">
+        <v>57</v>
+      </c>
+      <c r="C89" s="40" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="90" spans="2:3" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B90" s="22">
+        <v>58</v>
+      </c>
+      <c r="C90" s="40" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="91" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B91" s="22">
+        <v>61</v>
+      </c>
+      <c r="C91" s="40" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="92" spans="2:3" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B92" s="22">
+        <v>62</v>
+      </c>
+      <c r="C92" s="40" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="93" spans="2:3" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B93" s="22">
+        <v>63</v>
+      </c>
+      <c r="C93" s="40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="94" spans="2:3" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B94" s="22">
+        <v>64</v>
+      </c>
+      <c r="C94" s="40" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="95" spans="2:3" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B95" s="22">
+        <v>65</v>
+      </c>
+      <c r="C95" s="40" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="96" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B96" s="22">
+        <v>66</v>
+      </c>
+      <c r="C96" s="40" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="97" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B97" s="22">
+        <v>67</v>
+      </c>
+      <c r="C97" s="40" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="98" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B98" s="22">
+        <v>68</v>
+      </c>
+      <c r="C98" s="40" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="99" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B99" s="22">
+        <v>69</v>
+      </c>
+      <c r="C99" s="40" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="100" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B100" s="22">
+        <v>73</v>
+      </c>
+      <c r="C100" s="40" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="101" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B101" s="22">
+        <v>75</v>
+      </c>
+      <c r="C101" s="40" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="102" spans="2:3" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B102" s="22">
+        <v>76</v>
+      </c>
+      <c r="C102" s="40" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="103" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B103" s="22">
+        <v>111</v>
+      </c>
+      <c r="C103" s="40" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="104" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B104" s="22">
+        <v>142</v>
+      </c>
+      <c r="C104" s="40" t="s">
+        <v>375</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6310,18 +6899,18 @@
   <cols>
     <col min="1" max="1" width="45.125" customWidth="1"/>
     <col min="2" max="2" width="14" style="22" customWidth="1"/>
-    <col min="3" max="3" width="51.125" style="32" customWidth="1"/>
+    <col min="3" max="3" width="51.125" style="30" customWidth="1"/>
     <col min="4" max="4" width="49.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.5">
       <c r="A1" s="16" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>290</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="29" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="25" t="s">
@@ -6330,13 +6919,13 @@
     </row>
     <row r="2" spans="1:4" ht="37.5" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B2" s="24">
         <v>97</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>251</v>
@@ -6360,7 +6949,7 @@
         <v>120</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>142</v>
@@ -6371,7 +6960,7 @@
         <v>121</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>144</v>
@@ -6382,7 +6971,7 @@
         <v>122</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>146</v>
@@ -6404,7 +6993,7 @@
         <v>124</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>150</v>
@@ -6426,7 +7015,7 @@
         <v>126</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>270</v>
@@ -6448,7 +7037,7 @@
         <v>128</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>272</v>
@@ -6481,7 +7070,7 @@
         <v>133</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>164</v>
@@ -6499,18 +7088,18 @@
   <cols>
     <col min="1" max="1" width="37.25" customWidth="1"/>
     <col min="2" max="2" width="14.75" style="22" customWidth="1"/>
-    <col min="3" max="3" width="44" style="39" customWidth="1"/>
+    <col min="3" max="3" width="44" style="36" customWidth="1"/>
     <col min="4" max="4" width="51.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.5">
       <c r="A1" s="16" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>290</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="29" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="25" t="s">
@@ -6519,13 +7108,13 @@
     </row>
     <row r="2" spans="1:4" ht="37.5" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B2" s="24">
         <v>4</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>175</v>
@@ -6536,7 +7125,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>176</v>
@@ -6547,7 +7136,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>181</v>
@@ -6558,7 +7147,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>182</v>
@@ -6569,7 +7158,7 @@
         <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>185</v>
@@ -6580,7 +7169,7 @@
         <v>15</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>186</v>
@@ -6591,7 +7180,7 @@
         <v>16</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>187</v>
@@ -6602,7 +7191,7 @@
         <v>45</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>213</v>
@@ -6613,53 +7202,53 @@
         <v>46</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="37.5" x14ac:dyDescent="0.2">
-      <c r="B11" s="33">
+      <c r="B11" s="31">
         <v>48</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="C11" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="34" t="s">
+      <c r="D11" s="32" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="37.5" x14ac:dyDescent="0.2">
-      <c r="B12" s="33">
+      <c r="B12" s="31">
         <v>50</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" s="32" t="s">
         <v>288</v>
       </c>
-      <c r="D12" s="35" t="s">
+      <c r="D12" s="33" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="37.5" x14ac:dyDescent="0.2">
-      <c r="B13" s="33">
+      <c r="B13" s="31">
         <v>54</v>
       </c>
-      <c r="C13" s="34" t="s">
+      <c r="C13" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="D13" s="34" t="s">
+      <c r="D13" s="32" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="37.5" x14ac:dyDescent="0.2">
-      <c r="B14" s="33">
+      <c r="B14" s="31">
         <v>55</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="C14" s="32" t="s">
         <v>296</v>
       </c>
-      <c r="D14" s="35" t="s">
+      <c r="D14" s="33" t="s">
         <v>222</v>
       </c>
     </row>
@@ -6679,7 +7268,7 @@
         <v>120</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>142</v>
@@ -6690,7 +7279,7 @@
         <v>121</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>144</v>
@@ -6701,7 +7290,7 @@
         <v>122</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>146</v>
@@ -6712,20 +7301,20 @@
         <v>126</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="20" spans="2:4" ht="75" x14ac:dyDescent="0.2">
-      <c r="B20" s="33">
+      <c r="B20" s="31">
         <v>135</v>
       </c>
-      <c r="C20" s="34" t="s">
+      <c r="C20" s="32" t="s">
         <v>166</v>
       </c>
-      <c r="D20" s="35" t="s">
+      <c r="D20" s="33" t="s">
         <v>274</v>
       </c>
     </row>
@@ -6747,7 +7336,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.5">
       <c r="A1" s="16" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>290</v>
@@ -6765,7 +7354,7 @@
         <v>89</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>244</v>
@@ -6777,7 +7366,7 @@
         <v>90</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>106</v>
@@ -6789,7 +7378,7 @@
         <v>91</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>245</v>
@@ -6801,7 +7390,7 @@
         <v>92</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>246</v>
@@ -6813,7 +7402,7 @@
         <v>93</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>247</v>
@@ -6825,7 +7414,7 @@
         <v>94</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>248</v>
@@ -6837,7 +7426,7 @@
         <v>95</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>249</v>
@@ -6849,7 +7438,7 @@
         <v>96</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>250</v>
@@ -6861,7 +7450,7 @@
         <v>97</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>251</v>
@@ -6873,7 +7462,7 @@
         <v>98</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>252</v>
@@ -6885,7 +7474,7 @@
         <v>99</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>253</v>
@@ -6921,7 +7510,7 @@
         <v>102</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>256</v>
@@ -6933,7 +7522,7 @@
         <v>103</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>257</v>
@@ -6945,7 +7534,7 @@
         <v>104</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>258</v>
@@ -6957,7 +7546,7 @@
         <v>105</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>259</v>
@@ -6969,7 +7558,7 @@
         <v>107</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>260</v>
@@ -6981,7 +7570,7 @@
         <v>108</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>261</v>
@@ -6993,7 +7582,7 @@
         <v>81</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>239</v>
@@ -7005,7 +7594,7 @@
         <v>82</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>95</v>
@@ -7017,7 +7606,7 @@
         <v>83</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>240</v>
@@ -7029,7 +7618,7 @@
         <v>85</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>242</v>
@@ -7041,7 +7630,7 @@
         <v>86</v>
       </c>
       <c r="C25" s="24" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>243</v>
@@ -7074,7 +7663,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="37.5" x14ac:dyDescent="0.2">
@@ -7083,7 +7672,7 @@
         <v>20</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D2" s="20" t="s">
         <v>190</v>
@@ -7095,7 +7684,7 @@
         <v>59</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>64</v>
@@ -7107,7 +7696,7 @@
         <v>60</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D4" s="21" t="s">
         <v>66</v>
@@ -7119,7 +7708,7 @@
         <v>62</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D5" s="21" t="s">
         <v>70</v>
@@ -7131,7 +7720,7 @@
         <v>63</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D6" s="21" t="s">
         <v>72</v>
@@ -7143,7 +7732,7 @@
         <v>64</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D7" s="21" t="s">
         <v>74</v>
@@ -7155,7 +7744,7 @@
         <v>65</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D8" s="21" t="s">
         <v>76</v>
@@ -7167,7 +7756,7 @@
         <v>66</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D9" s="20" t="s">
         <v>225</v>
@@ -7179,7 +7768,7 @@
         <v>68</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D10" s="21" t="s">
         <v>226</v>
@@ -7191,7 +7780,7 @@
         <v>71</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D11" s="21" t="s">
         <v>229</v>
@@ -7203,7 +7792,7 @@
         <v>72</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D12" s="21" t="s">
         <v>230</v>
@@ -7215,7 +7804,7 @@
         <v>73</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D13" s="20" t="s">
         <v>231</v>
@@ -7227,7 +7816,7 @@
         <v>75</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D14" s="20" t="s">
         <v>233</v>
@@ -7239,7 +7828,7 @@
         <v>115</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D15" s="21" t="s">
         <v>135</v>
@@ -7251,7 +7840,7 @@
         <v>116</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D16" s="21" t="s">
         <v>266</v>
@@ -7263,7 +7852,7 @@
         <v>117</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D17" s="20" t="s">
         <v>267</v>
